--- a/extenbooks/ES2301_extenbook.xlsx
+++ b/extenbooks/ES2301_extenbook.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A137"/>
+  <dimension ref="A1:A160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -902,7 +902,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>## 6. Census-basis vs BoP-basis</t>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,177 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Paper Fig 1 footnote: "Total Exports Value minus Customs Import Value".</t>
+          <t>The extension proxy `Census FT900 Exhibit 1 (world) + c5700 (China)` measures</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>This is the Census basis (not BoP basis). We reproduce Census basis to</t>
+          <t>`US merchandise (goods) trade balance, Census basis` rather than</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>match paper recipe; BEA International Transactions Table 4.1 BoP-basis</t>
+          <t>`US current account` or `BoP-basis goods balance` because:</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>goods balance is concept-adjacent but methodologically distinct.</t>
+          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 1 explicitly cites Census,</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  not BEA International Transactions. Census FT900 is the published recipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: paper-window 2002-2017 values were Census-basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  monthly aggregates; 2018-2024 extension uses the *same* FT900 release</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (same agency, same exhibit numbers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>- Disambiguation: Census-basis (Total Exports Value − Customs Import Value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  differs from BoP-basis (BEA ITA Table 4.1, which makes balance-of-payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  coverage and timing adjustments), and from current-account (which adds</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  services, primary income, and secondary income).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>The book's original concept (paper p. 432, Fig 1 footnote) was: "Total Exports</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Value minus Customs Import Value". The modern series preserves Census-basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>goods coverage and the bilateral US-China decomposition while permitting a</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>small post-2018 Section-301-tariff valuation effect (customs values now</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>include tariff-inclusive imports for some HTS lines). This is NOT a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>substitution forbidden by the No-Proxy rule because the loader pulls from</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>*exactly* the source the paper cites (US Census FT900) — no agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>substitution, no concept substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>## 7. Method note: Census-basis vs BoP-basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>We reproduce Census basis to match paper recipe; BEA International</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Transactions Table 4.1 BoP-basis goods balance is concept-adjacent but</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>methodologically distinct and is NOT used.</t>
         </is>
       </c>
     </row>
@@ -2006,11 +2155,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2033,54 +2182,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2301_DPR.md", "epr": "Technical/docs/series/ES2301_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2301_load.py", "processor": "Technical/code/P02_processors/P02_ES2301_construct.py", "validator": "Technical/code/V03_validators/V03_ES2301_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
